--- a/results/greedy/UAVs8_GRID13/revenue/UAVs8_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs8_GRID13/revenue/UAVs8_GRID13_Greedy.xlsx
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0224674170021899</v>
+        <v>0.02370829100254923</v>
       </c>
       <c r="C2" t="n">
         <v>17.64156561900313</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932045899797231</v>
+        <v>0.02835066599072888</v>
       </c>
       <c r="C2" t="n">
         <v>22.67306938793612</v>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02399454201804474</v>
+        <v>0.02259466703981161</v>
       </c>
       <c r="C2" t="n">
         <v>17.78186918708691</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02508416696218774</v>
+        <v>0.02461170899914578</v>
       </c>
       <c r="C2" t="n">
         <v>27.55248750187481</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02881166600855067</v>
+        <v>0.02879850001772866</v>
       </c>
       <c r="C2" t="n">
         <v>25.59545572906268</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02735091699287295</v>
+        <v>0.02706970798317343</v>
       </c>
       <c r="C2" t="n">
         <v>20.61246363515794</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02226350002456456</v>
+        <v>0.02172637503826991</v>
       </c>
       <c r="C2" t="n">
         <v>20.98588451917151</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02603062498383224</v>
+        <v>0.0252170410240069</v>
       </c>
       <c r="C2" t="n">
         <v>19.69448401920375</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01959683297900483</v>
+        <v>0.01936249999562278</v>
       </c>
       <c r="C2" t="n">
         <v>19.71345180645848</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01940970902796835</v>
+        <v>0.01992349995998666</v>
       </c>
       <c r="C2" t="n">
         <v>22.86910168994165</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02485350001370534</v>
+        <v>0.02432645799126476</v>
       </c>
       <c r="C2" t="n">
         <v>26.14047960663754</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02428095805225894</v>
+        <v>0.02401358296629041</v>
       </c>
       <c r="C2" t="n">
         <v>20.38450452769923</v>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02372533298330382</v>
+        <v>0.02432170801330358</v>
       </c>
       <c r="C2" t="n">
         <v>17.26899024640831</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02633508399594575</v>
+        <v>0.02662600000621751</v>
       </c>
       <c r="C2" t="n">
         <v>20.2261153734274</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02523654204560444</v>
+        <v>0.02495704096509144</v>
       </c>
       <c r="C2" t="n">
         <v>18.47592729336636</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02228545799152926</v>
+        <v>0.02174804196693003</v>
       </c>
       <c r="C2" t="n">
         <v>21.57370717537049</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02170541702071205</v>
+        <v>0.02205133304232731</v>
       </c>
       <c r="C2" t="n">
         <v>23.89483437692984</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0251744159613736</v>
+        <v>0.02727050002431497</v>
       </c>
       <c r="C2" t="n">
         <v>22.81485902268702</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02648741699522361</v>
+        <v>0.02724795899121091</v>
       </c>
       <c r="C2" t="n">
         <v>25.47292043886102</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023541700327769</v>
+        <v>0.0200036249589175</v>
       </c>
       <c r="C2" t="n">
         <v>19.04592757106387</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02211845899000764</v>
+        <v>0.02190833300119266</v>
       </c>
       <c r="C2" t="n">
         <v>16.4777047806555</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02721629198640585</v>
+        <v>0.02761345799081028</v>
       </c>
       <c r="C2" t="n">
         <v>23.10281869892845</v>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02832116698846221</v>
+        <v>0.0277420420316048</v>
       </c>
       <c r="C2" t="n">
         <v>24.39754891290769</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02648670802591369</v>
+        <v>0.0274296670104377</v>
       </c>
       <c r="C2" t="n">
         <v>20.66968301258062</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02579241700004786</v>
+        <v>0.02577400003792718</v>
       </c>
       <c r="C2" t="n">
         <v>18.51561482689536</v>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02307175000896677</v>
+        <v>0.02331679104827344</v>
       </c>
       <c r="C2" t="n">
         <v>19.96567370405879</v>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02066112495958805</v>
+        <v>0.02033645904157311</v>
       </c>
       <c r="C2" t="n">
         <v>20.28763145474303</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.024465250025969</v>
+        <v>0.02563774998998269</v>
       </c>
       <c r="C2" t="n">
         <v>19.33861720606609</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01895375002641231</v>
+        <v>0.01967616699403152</v>
       </c>
       <c r="C2" t="n">
         <v>17.37146471931447</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02497816696995869</v>
+        <v>0.02468549995683134</v>
       </c>
       <c r="C2" t="n">
         <v>21.16588845069946</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330600004643202</v>
+        <v>0.02369133400497958</v>
       </c>
       <c r="C2" t="n">
         <v>24.08897987083291</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02264354203362018</v>
+        <v>0.02254258305765688</v>
       </c>
       <c r="C2" t="n">
         <v>17.87689949063981</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02041429199744016</v>
+        <v>0.02070191700477153</v>
       </c>
       <c r="C2" t="n">
         <v>19.32041480573725</v>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0261858330341056</v>
+        <v>0.02575050003360957</v>
       </c>
       <c r="C2" t="n">
         <v>23.75067920199727</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02636937500210479</v>
+        <v>0.02718437497969717</v>
       </c>
       <c r="C2" t="n">
         <v>21.28618254149552</v>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02532616700045764</v>
+        <v>0.03463154099881649</v>
       </c>
       <c r="C2" t="n">
         <v>21.26793111050785</v>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02446150005562231</v>
+        <v>0.02407362504163757</v>
       </c>
       <c r="C2" t="n">
         <v>20.1710791130888</v>
@@ -4198,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0216537500382401</v>
+        <v>0.02163479197770357</v>
       </c>
       <c r="C2" t="n">
         <v>23.76229839876511</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02764395897975191</v>
+        <v>0.02734054200118408</v>
       </c>
       <c r="C2" t="n">
         <v>26.07879270163025</v>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01936595799634233</v>
+        <v>0.02217904198914766</v>
       </c>
       <c r="C2" t="n">
         <v>17.1820278091804</v>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01750704098958522</v>
+        <v>0.0206299580167979</v>
       </c>
       <c r="C2" t="n">
         <v>19.36611514824218</v>
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01847462495788932</v>
+        <v>0.0191565829445608</v>
       </c>
       <c r="C2" t="n">
         <v>23.27530579480145</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02065691701136529</v>
+        <v>0.02246516599552706</v>
       </c>
       <c r="C2" t="n">
         <v>15.01780092030665</v>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02318300004117191</v>
+        <v>0.02296741597820073</v>
       </c>
       <c r="C2" t="n">
         <v>17.96035386552563</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02359987498493865</v>
+        <v>0.02521383401472121</v>
       </c>
       <c r="C2" t="n">
         <v>17.31160729717415</v>
@@ -4982,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276970900129527</v>
+        <v>0.02256820804905146</v>
       </c>
       <c r="C2" t="n">
         <v>19.28895719098222</v>
@@ -5080,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02119391702581197</v>
+        <v>0.02895220898790285</v>
       </c>
       <c r="C2" t="n">
         <v>19.56424777497094</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02216804202180356</v>
+        <v>0.04011829098453745</v>
       </c>
       <c r="C2" t="n">
         <v>25.23207762676086</v>
@@ -5276,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02522695902734995</v>
+        <v>0.02510104200337082</v>
       </c>
       <c r="C2" t="n">
         <v>14.32324938089149</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02465445903362706</v>
+        <v>0.02547925000544637</v>
       </c>
       <c r="C2" t="n">
         <v>22.15213457387565</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023920899955556</v>
+        <v>0.02240945800440386</v>
       </c>
       <c r="C2" t="n">
         <v>21.53572740990238</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01887283398536965</v>
+        <v>0.0194754580152221</v>
       </c>
       <c r="C2" t="n">
         <v>18.82204974577217</v>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02325954200932756</v>
+        <v>0.04090437496779487</v>
       </c>
       <c r="C2" t="n">
         <v>22.3400986282424</v>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02110166702186689</v>
+        <v>0.02087820798624307</v>
       </c>
       <c r="C2" t="n">
         <v>18.39040837911605</v>
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02102520799962804</v>
+        <v>0.02053891698596999</v>
       </c>
       <c r="C2" t="n">
         <v>28.06446122627381</v>
@@ -5962,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387570805149153</v>
+        <v>0.02761195896891877</v>
       </c>
       <c r="C2" t="n">
         <v>20.44975046602345</v>
@@ -6060,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02693520800676197</v>
+        <v>0.02687770797638223</v>
       </c>
       <c r="C2" t="n">
         <v>21.7993092702801</v>
@@ -6158,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01766858296468854</v>
+        <v>0.01731541700428352</v>
       </c>
       <c r="C2" t="n">
         <v>25.58225517261277</v>
@@ -6256,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388454199535772</v>
+        <v>0.02333533402998</v>
       </c>
       <c r="C2" t="n">
         <v>21.11266512443118</v>
@@ -6354,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02030587499029934</v>
+        <v>0.01983424997888505</v>
       </c>
       <c r="C2" t="n">
         <v>15.9707045592019</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02035604103002697</v>
+        <v>0.01987320894841105</v>
       </c>
       <c r="C2" t="n">
         <v>22.00377786716665</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0292802500189282</v>
+        <v>0.02918987500015646</v>
       </c>
       <c r="C2" t="n">
         <v>20.13385000639834</v>
@@ -6648,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.028609958011657</v>
+        <v>0.02838204201543704</v>
       </c>
       <c r="C2" t="n">
         <v>22.67800137788619</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02702570799738169</v>
+        <v>0.02627899998333305</v>
       </c>
       <c r="C2" t="n">
         <v>19.76878426848157</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01897387497592717</v>
+        <v>0.01921549998223782</v>
       </c>
       <c r="C2" t="n">
         <v>18.74597180368235</v>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01991062500746921</v>
+        <v>0.02030995895620435</v>
       </c>
       <c r="C2" t="n">
         <v>20.46579633007225</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02427962503861636</v>
+        <v>0.02396558300824836</v>
       </c>
       <c r="C2" t="n">
         <v>20.69331842407136</v>
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02480479096993804</v>
+        <v>0.0244318749755621</v>
       </c>
       <c r="C2" t="n">
         <v>25.90891689704868</v>
@@ -7236,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02366595802595839</v>
+        <v>0.02335095900343731</v>
       </c>
       <c r="C2" t="n">
         <v>22.96933709913643</v>
@@ -7334,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02716733299894258</v>
+        <v>0.02923945803195238</v>
       </c>
       <c r="C2" t="n">
         <v>25.06999331842455</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02776795800309628</v>
+        <v>0.02774858300108463</v>
       </c>
       <c r="C2" t="n">
         <v>18.86455204642904</v>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02072700002463534</v>
+        <v>0.02045020798686892</v>
       </c>
       <c r="C2" t="n">
         <v>17.46192971855275</v>
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02288537501590326</v>
+        <v>0.0226302079972811</v>
       </c>
       <c r="C2" t="n">
         <v>15.24861797149014</v>
@@ -7726,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02316758298547938</v>
+        <v>0.02392141701420769</v>
       </c>
       <c r="C2" t="n">
         <v>21.40286303144538</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01715545903425664</v>
+        <v>0.01819495903328061</v>
       </c>
       <c r="C2" t="n">
         <v>24.98758994819316</v>
@@ -7922,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02172899997094646</v>
+        <v>0.02209041605237871</v>
       </c>
       <c r="C2" t="n">
         <v>21.72616195554193</v>
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02860470896121114</v>
+        <v>0.02850312500959262</v>
       </c>
       <c r="C2" t="n">
         <v>17.92678684798167</v>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02372999995714054</v>
+        <v>0.024384958029259</v>
       </c>
       <c r="C2" t="n">
         <v>19.03476700520275</v>
@@ -8216,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01532075001159683</v>
+        <v>0.01525699999183416</v>
       </c>
       <c r="C2" t="n">
         <v>16.95800260777418</v>
@@ -8314,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02610158396419138</v>
+        <v>0.0268787500099279</v>
       </c>
       <c r="C2" t="n">
         <v>19.87748998971347</v>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02580170897999778</v>
+        <v>0.03355724998982623</v>
       </c>
       <c r="C2" t="n">
         <v>23.36216586592385</v>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02156987501075491</v>
+        <v>0.02288154099369422</v>
       </c>
       <c r="C2" t="n">
         <v>20.03695291332611</v>
@@ -8608,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02409179101232439</v>
+        <v>0.02349475002847612</v>
       </c>
       <c r="C2" t="n">
         <v>23.12593054474433</v>
@@ -8706,7 +8706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02035220799734816</v>
+        <v>0.02092375000938773</v>
       </c>
       <c r="C2" t="n">
         <v>14.28122114975867</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02630337496520951</v>
+        <v>0.02605079195927829</v>
       </c>
       <c r="C2" t="n">
         <v>24.87729051742816</v>
@@ -8902,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02358195901615545</v>
+        <v>0.02332666702568531</v>
       </c>
       <c r="C2" t="n">
         <v>20.65835187846175</v>
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02689824998378754</v>
+        <v>0.02710683300392702</v>
       </c>
       <c r="C2" t="n">
         <v>17.64153561615723</v>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02774120902176946</v>
+        <v>0.02946791599970311</v>
       </c>
       <c r="C2" t="n">
         <v>21.57308107405452</v>
@@ -9196,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03380862501217052</v>
+        <v>0.03306908399099484</v>
       </c>
       <c r="C2" t="n">
         <v>21.25303530401116</v>
@@ -9294,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02392762503586709</v>
+        <v>0.03986387501936406</v>
       </c>
       <c r="C2" t="n">
         <v>21.94014777938318</v>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0195541669963859</v>
+        <v>0.01925995800411329</v>
       </c>
       <c r="C2" t="n">
         <v>19.88904349968421</v>
@@ -9490,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02705720899393782</v>
+        <v>0.02634758298518136</v>
       </c>
       <c r="C2" t="n">
         <v>21.80803098635583</v>
@@ -9588,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02206720795948058</v>
+        <v>0.02168904099380597</v>
       </c>
       <c r="C2" t="n">
         <v>20.4975612670904</v>
@@ -9686,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02497637498890981</v>
+        <v>0.0243458750192076</v>
       </c>
       <c r="C2" t="n">
         <v>18.9712759702732</v>
@@ -9784,7 +9784,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02445791702484712</v>
+        <v>0.02410483302082866</v>
       </c>
       <c r="C2" t="n">
         <v>20.9457820529186</v>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02311499998904765</v>
+        <v>0.02405462501337752</v>
       </c>
       <c r="C2" t="n">
         <v>13.40160208559052</v>
@@ -9980,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02443395805312321</v>
+        <v>0.0241453749476932</v>
       </c>
       <c r="C2" t="n">
         <v>29.11478943835019</v>
@@ -10078,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03014595899730921</v>
+        <v>0.02979562495602295</v>
       </c>
       <c r="C2" t="n">
         <v>24.44745416266226</v>
@@ -10176,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387087501119822</v>
+        <v>0.02330266701756045</v>
       </c>
       <c r="C2" t="n">
         <v>19.85576657039149</v>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0241272080456838</v>
+        <v>0.02369066601386294</v>
       </c>
       <c r="C2" t="n">
         <v>20.89428504453298</v>

--- a/results/greedy/UAVs8_GRID13/revenue/UAVs8_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs8_GRID13/revenue/UAVs8_GRID13_Greedy.xlsx
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02370829100254923</v>
+        <v>0.02242045802995563</v>
       </c>
       <c r="C2" t="n">
         <v>17.64156561900313</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02835066599072888</v>
+        <v>0.02881420898484066</v>
       </c>
       <c r="C2" t="n">
         <v>22.67306938793612</v>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02259466703981161</v>
+        <v>0.02234908397076651</v>
       </c>
       <c r="C2" t="n">
         <v>17.78186918708691</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02461170899914578</v>
+        <v>0.02493800001684576</v>
       </c>
       <c r="C2" t="n">
         <v>27.55248750187481</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02879850001772866</v>
+        <v>0.02818741695955396</v>
       </c>
       <c r="C2" t="n">
         <v>25.59545572906268</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02706970798317343</v>
+        <v>0.02668099995935336</v>
       </c>
       <c r="C2" t="n">
         <v>20.61246363515794</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02172637503826991</v>
+        <v>0.02149233297677711</v>
       </c>
       <c r="C2" t="n">
         <v>20.98588451917151</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252170410240069</v>
+        <v>0.02676587499445304</v>
       </c>
       <c r="C2" t="n">
         <v>19.69448401920375</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01936249999562278</v>
+        <v>0.01883770799031481</v>
       </c>
       <c r="C2" t="n">
         <v>19.71345180645848</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01992349995998666</v>
+        <v>0.01878604100784287</v>
       </c>
       <c r="C2" t="n">
         <v>22.86910168994165</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02432645799126476</v>
+        <v>0.02466979197924957</v>
       </c>
       <c r="C2" t="n">
         <v>26.14047960663754</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401358296629041</v>
+        <v>0.02376529097091407</v>
       </c>
       <c r="C2" t="n">
         <v>20.38450452769923</v>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02432170801330358</v>
+        <v>0.02304254099726677</v>
       </c>
       <c r="C2" t="n">
         <v>17.26899024640831</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02662600000621751</v>
+        <v>0.02583224995760247</v>
       </c>
       <c r="C2" t="n">
         <v>20.2261153734274</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02495704096509144</v>
+        <v>0.02490729198325425</v>
       </c>
       <c r="C2" t="n">
         <v>18.47592729336636</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02174804196693003</v>
+        <v>0.02153091697255149</v>
       </c>
       <c r="C2" t="n">
         <v>21.57370717537049</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02205133304232731</v>
+        <v>0.02117429202189669</v>
       </c>
       <c r="C2" t="n">
         <v>23.89483437692984</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02727050002431497</v>
+        <v>0.02477587503381073</v>
       </c>
       <c r="C2" t="n">
         <v>22.81485902268702</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02724795899121091</v>
+        <v>0.02630833303555846</v>
       </c>
       <c r="C2" t="n">
         <v>25.47292043886102</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0200036249589175</v>
+        <v>0.01964924996718764</v>
       </c>
       <c r="C2" t="n">
         <v>19.04592757106387</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02190833300119266</v>
+        <v>0.0213653749669902</v>
       </c>
       <c r="C2" t="n">
         <v>16.4777047806555</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761345799081028</v>
+        <v>0.02726029098266736</v>
       </c>
       <c r="C2" t="n">
         <v>23.10281869892845</v>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0277420420316048</v>
+        <v>0.02745149994734675</v>
       </c>
       <c r="C2" t="n">
         <v>24.39754891290769</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0274296670104377</v>
+        <v>0.0259606660110876</v>
       </c>
       <c r="C2" t="n">
         <v>20.66968301258062</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02577400003792718</v>
+        <v>0.02521441702265292</v>
       </c>
       <c r="C2" t="n">
         <v>18.51561482689536</v>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02331679104827344</v>
+        <v>0.02253204100998119</v>
       </c>
       <c r="C2" t="n">
         <v>19.96567370405879</v>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02033645904157311</v>
+        <v>0.02022641699295491</v>
       </c>
       <c r="C2" t="n">
         <v>20.28763145474303</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02563774998998269</v>
+        <v>0.02354708302300423</v>
       </c>
       <c r="C2" t="n">
         <v>19.33861720606609</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01967616699403152</v>
+        <v>0.01841354096541181</v>
       </c>
       <c r="C2" t="n">
         <v>17.37146471931447</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02468549995683134</v>
+        <v>0.02471612504450604</v>
       </c>
       <c r="C2" t="n">
         <v>21.16588845069946</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02369133400497958</v>
+        <v>0.02289383299648762</v>
       </c>
       <c r="C2" t="n">
         <v>24.08897987083291</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02254258305765688</v>
+        <v>0.0221787909977138</v>
       </c>
       <c r="C2" t="n">
         <v>17.87689949063981</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02070191700477153</v>
+        <v>0.02093120798235759</v>
       </c>
       <c r="C2" t="n">
         <v>19.32041480573725</v>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02575050003360957</v>
+        <v>0.02583054103888571</v>
       </c>
       <c r="C2" t="n">
         <v>23.75067920199727</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02718437497969717</v>
+        <v>0.02627283299807459</v>
       </c>
       <c r="C2" t="n">
         <v>21.28618254149552</v>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03463154099881649</v>
+        <v>0.02529687498463318</v>
       </c>
       <c r="C2" t="n">
         <v>21.26793111050785</v>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02407362504163757</v>
+        <v>0.0239944169879891</v>
       </c>
       <c r="C2" t="n">
         <v>20.1710791130888</v>
@@ -4198,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02163479197770357</v>
+        <v>0.02210066700354218</v>
       </c>
       <c r="C2" t="n">
         <v>23.76229839876511</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02734054200118408</v>
+        <v>0.02791695803171024</v>
       </c>
       <c r="C2" t="n">
         <v>26.07879270163025</v>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02217904198914766</v>
+        <v>0.01980170799652115</v>
       </c>
       <c r="C2" t="n">
         <v>17.1820278091804</v>
@@ -4492,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0206299580167979</v>
+        <v>0.01708174997474998</v>
       </c>
       <c r="C2" t="n">
         <v>19.36611514824218</v>
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0191565829445608</v>
+        <v>0.01805300003616139</v>
       </c>
       <c r="C2" t="n">
         <v>23.27530579480145</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02246516599552706</v>
+        <v>0.02081641700351611</v>
       </c>
       <c r="C2" t="n">
         <v>15.01780092030665</v>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02296741597820073</v>
+        <v>0.02280541695654392</v>
       </c>
       <c r="C2" t="n">
         <v>17.96035386552563</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02521383401472121</v>
+        <v>0.02380745799746364</v>
       </c>
       <c r="C2" t="n">
         <v>17.31160729717415</v>
@@ -4982,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02256820804905146</v>
+        <v>0.02272695902502164</v>
       </c>
       <c r="C2" t="n">
         <v>19.28895719098222</v>
@@ -5080,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02895220898790285</v>
+        <v>0.02159404201665893</v>
       </c>
       <c r="C2" t="n">
         <v>19.56424777497094</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04011829098453745</v>
+        <v>0.02161674998933449</v>
       </c>
       <c r="C2" t="n">
         <v>25.23207762676086</v>
@@ -5276,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02510104200337082</v>
+        <v>0.02509650000138208</v>
       </c>
       <c r="C2" t="n">
         <v>14.32324938089149</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02547925000544637</v>
+        <v>0.02502433402696624</v>
       </c>
       <c r="C2" t="n">
         <v>22.15213457387565</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02240945800440386</v>
+        <v>0.02082295902073383</v>
       </c>
       <c r="C2" t="n">
         <v>21.53572740990238</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0194754580152221</v>
+        <v>0.01980670902412385</v>
       </c>
       <c r="C2" t="n">
         <v>18.82204974577217</v>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04090437496779487</v>
+        <v>0.02296941704116762</v>
       </c>
       <c r="C2" t="n">
         <v>22.3400986282424</v>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02087820798624307</v>
+        <v>0.0206593339680694</v>
       </c>
       <c r="C2" t="n">
         <v>18.39040837911605</v>
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02053891698596999</v>
+        <v>0.02080508298240602</v>
       </c>
       <c r="C2" t="n">
         <v>28.06446122627381</v>
@@ -5962,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761195896891877</v>
+        <v>0.02363166701979935</v>
       </c>
       <c r="C2" t="n">
         <v>20.44975046602345</v>
@@ -6060,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02687770797638223</v>
+        <v>0.02787425002316013</v>
       </c>
       <c r="C2" t="n">
         <v>21.7993092702801</v>
@@ -6158,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01731541700428352</v>
+        <v>0.01821154198842123</v>
       </c>
       <c r="C2" t="n">
         <v>25.58225517261277</v>
@@ -6256,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02333533402998</v>
+        <v>0.02361316699534655</v>
       </c>
       <c r="C2" t="n">
         <v>21.11266512443118</v>
@@ -6354,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01983424997888505</v>
+        <v>0.02059004199691117</v>
       </c>
       <c r="C2" t="n">
         <v>15.9707045592019</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01987320894841105</v>
+        <v>0.0201097919489257</v>
       </c>
       <c r="C2" t="n">
         <v>22.00377786716665</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02918987500015646</v>
+        <v>0.02879987499909475</v>
       </c>
       <c r="C2" t="n">
         <v>20.13385000639834</v>
@@ -6648,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02838204201543704</v>
+        <v>0.02798116696067154</v>
       </c>
       <c r="C2" t="n">
         <v>22.67800137788619</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627899998333305</v>
+        <v>0.02661266596987844</v>
       </c>
       <c r="C2" t="n">
         <v>19.76878426848157</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01921549998223782</v>
+        <v>0.01900224998826161</v>
       </c>
       <c r="C2" t="n">
         <v>18.74597180368235</v>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02030995895620435</v>
+        <v>0.0203281250433065</v>
       </c>
       <c r="C2" t="n">
         <v>20.46579633007225</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02396558300824836</v>
+        <v>0.02502133295638487</v>
       </c>
       <c r="C2" t="n">
         <v>20.69331842407136</v>
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0244318749755621</v>
+        <v>0.02481258398620412</v>
       </c>
       <c r="C2" t="n">
         <v>25.90891689704868</v>
@@ -7236,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02335095900343731</v>
+        <v>0.02473879099125043</v>
       </c>
       <c r="C2" t="n">
         <v>22.96933709913643</v>
@@ -7334,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02923945803195238</v>
+        <v>0.02742087497608736</v>
       </c>
       <c r="C2" t="n">
         <v>25.06999331842455</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02774858300108463</v>
+        <v>0.02725941699463874</v>
       </c>
       <c r="C2" t="n">
         <v>18.86455204642904</v>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02045020798686892</v>
+        <v>0.02108570898417383</v>
       </c>
       <c r="C2" t="n">
         <v>17.46192971855275</v>
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0226302079972811</v>
+        <v>0.02296699996804819</v>
       </c>
       <c r="C2" t="n">
         <v>15.24861797149014</v>
@@ -7726,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02392141701420769</v>
+        <v>0.02346570894587785</v>
       </c>
       <c r="C2" t="n">
         <v>21.40286303144538</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01819495903328061</v>
+        <v>0.01776191702811047</v>
       </c>
       <c r="C2" t="n">
         <v>24.98758994819316</v>
@@ -7922,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02209041605237871</v>
+        <v>0.02229074999922886</v>
       </c>
       <c r="C2" t="n">
         <v>21.72616195554193</v>
@@ -8020,7 +8020,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02850312500959262</v>
+        <v>0.02827454201178625</v>
       </c>
       <c r="C2" t="n">
         <v>17.92678684798167</v>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.024384958029259</v>
+        <v>0.02338774997042492</v>
       </c>
       <c r="C2" t="n">
         <v>19.03476700520275</v>
@@ -8216,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01525699999183416</v>
+        <v>0.01517133397283033</v>
       </c>
       <c r="C2" t="n">
         <v>16.95800260777418</v>
@@ -8314,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0268787500099279</v>
+        <v>0.02615120896371081</v>
       </c>
       <c r="C2" t="n">
         <v>19.87748998971347</v>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03355724998982623</v>
+        <v>0.02528179198270664</v>
       </c>
       <c r="C2" t="n">
         <v>23.36216586592385</v>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02288154099369422</v>
+        <v>0.02112275001127273</v>
       </c>
       <c r="C2" t="n">
         <v>20.03695291332611</v>
@@ -8608,7 +8608,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02349475002847612</v>
+        <v>0.02310383302392438</v>
       </c>
       <c r="C2" t="n">
         <v>23.12593054474433</v>
@@ -8706,7 +8706,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02092375000938773</v>
+        <v>0.01989554200554267</v>
       </c>
       <c r="C2" t="n">
         <v>14.28122114975867</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02605079195927829</v>
+        <v>0.02588841697433963</v>
       </c>
       <c r="C2" t="n">
         <v>24.87729051742816</v>
@@ -8902,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02332666702568531</v>
+        <v>0.02351649996126071</v>
       </c>
       <c r="C2" t="n">
         <v>20.65835187846175</v>
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02710683300392702</v>
+        <v>0.02723733300808817</v>
       </c>
       <c r="C2" t="n">
         <v>17.64153561615723</v>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02946791599970311</v>
+        <v>0.02726404200075194</v>
       </c>
       <c r="C2" t="n">
         <v>21.57308107405452</v>
@@ -9196,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03306908399099484</v>
+        <v>0.03300837497226894</v>
       </c>
       <c r="C2" t="n">
         <v>21.25303530401116</v>
@@ -9294,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03986387501936406</v>
+        <v>0.02326550002908334</v>
       </c>
       <c r="C2" t="n">
         <v>21.94014777938318</v>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01925995800411329</v>
+        <v>0.01960041699931026</v>
       </c>
       <c r="C2" t="n">
         <v>19.88904349968421</v>
@@ -9490,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02634758298518136</v>
+        <v>0.02655220800079405</v>
       </c>
       <c r="C2" t="n">
         <v>21.80803098635583</v>
@@ -9588,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02168904099380597</v>
+        <v>0.02178037504199892</v>
       </c>
       <c r="C2" t="n">
         <v>20.4975612670904</v>
@@ -9686,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0243458750192076</v>
+        <v>0.02409625001018867</v>
       </c>
       <c r="C2" t="n">
         <v>18.9712759702732</v>
@@ -9784,7 +9784,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02410483302082866</v>
+        <v>0.02387025003554299</v>
       </c>
       <c r="C2" t="n">
         <v>20.9457820529186</v>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02405462501337752</v>
+        <v>0.02249995898455381</v>
       </c>
       <c r="C2" t="n">
         <v>13.40160208559052</v>
@@ -9980,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0241453749476932</v>
+        <v>0.02353916695574299</v>
       </c>
       <c r="C2" t="n">
         <v>29.11478943835019</v>
@@ -10078,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02979562495602295</v>
+        <v>0.02944445802131668</v>
       </c>
       <c r="C2" t="n">
         <v>24.44745416266226</v>
@@ -10176,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330266701756045</v>
+        <v>0.02322824997827411</v>
       </c>
       <c r="C2" t="n">
         <v>19.85576657039149</v>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02369066601386294</v>
+        <v>0.02377024997258559</v>
       </c>
       <c r="C2" t="n">
         <v>20.89428504453298</v>
